--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFARBillStatus.xlsx
+++ b/docs/CMVFARBillStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
